--- a/duoki_editor/resources/data/blank/海洋-魔法师-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/海洋-魔法师-1-blank.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
   <si>
     <t>stage_id</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>寻找东西任务_第4次</t>
+  </si>
+  <si>
+    <t>寻找东西任务_帮助</t>
   </si>
   <si>
     <t>(生成图片_提示词)</t>
@@ -492,10 +495,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -509,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -526,10 +529,10 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -543,10 +546,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -560,10 +563,10 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -577,10 +580,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -591,13 +594,13 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -608,10 +611,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>200615</v>
@@ -625,13 +628,13 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -642,13 +645,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
